--- a/CHARMS MURANOS.xlsx
+++ b/CHARMS MURANOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1EB11F-19D5-40F8-B85E-AE7435C88BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EACD69-F822-4E2B-A503-ADDA108CBA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C24915DC-4ECB-423C-AEB0-A167D944F2DF}"/>
   </bookViews>
@@ -7521,7 +7521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A37F042D-38C3-47B8-AE70-DD3B2673CF38}">
-  <dimension ref="A1:K296"/>
+  <dimension ref="A1:K295"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
@@ -7642,11 +7642,11 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10">
         <v>2</v>
       </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
@@ -7833,11 +7833,11 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10">
         <v>2</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
@@ -7864,9 +7864,7 @@
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
-      <c r="K12" s="10">
-        <v>1</v>
-      </c>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
@@ -7945,11 +7943,11 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10">
         <v>1</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
     </row>
     <row r="16" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
@@ -12079,7 +12077,6 @@
     <row r="293" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="294" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="295" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
